--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.13765188875988</v>
+        <v>1.15986843192348</v>
       </c>
       <c r="D2" t="n">
-        <v>7.146372638361095</v>
+        <v>1.161285553733678</v>
       </c>
       <c r="E2" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F2" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.26634698756369</v>
+        <v>4.430781385479101</v>
       </c>
       <c r="D3" t="n">
-        <v>23.59863596284434</v>
+        <v>3.834778343962205</v>
       </c>
       <c r="E3" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F3" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.71347215387634</v>
+        <v>3.365939225004906</v>
       </c>
       <c r="D4" t="n">
-        <v>21.1019321146196</v>
+        <v>3.429063968625686</v>
       </c>
       <c r="E4" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F4" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.70952519575143</v>
+        <v>3.527797844309607</v>
       </c>
       <c r="D5" t="n">
-        <v>21.53095995640771</v>
+        <v>3.498780992916254</v>
       </c>
       <c r="E5" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F5" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.41855261992745</v>
+        <v>3.31801480073821</v>
       </c>
       <c r="D6" t="n">
-        <v>22.27666940994546</v>
+        <v>3.619958779116138</v>
       </c>
       <c r="E6" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F6" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.68297898995065</v>
+        <v>2.54848408586698</v>
       </c>
       <c r="D7" t="n">
-        <v>24.56318435317322</v>
+        <v>3.991517457390649</v>
       </c>
       <c r="E7" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F7" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.2909749974902</v>
+        <v>3.134783437092158</v>
       </c>
       <c r="D8" t="n">
-        <v>18.41456003975534</v>
+        <v>2.992366006460244</v>
       </c>
       <c r="E8" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F8" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.46285493143316</v>
+        <v>5.600213926357889</v>
       </c>
       <c r="D9" t="n">
-        <v>10.31264232464097</v>
+        <v>1.675804377754157</v>
       </c>
       <c r="E9" t="n">
-        <v>7.454682455882724</v>
+        <v>1.211385899080943</v>
       </c>
       <c r="F9" t="n">
-        <v>6.008448801890102</v>
+        <v>0.9763729303071417</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
